--- a/branches/dependabot/github_actions/dev/actions-3dcd9e0407/StructureDefinition-mii-pr-icu-muv-arterieller-blutdruck.xlsx
+++ b/branches/dependabot/github_actions/dev/actions-3dcd9e0407/StructureDefinition-mii-pr-icu-muv-arterieller-blutdruck.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T22:29:54+00:00</t>
+    <t>2026-10-26T22:31:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dependabot/github_actions/dev/actions-3dcd9e0407/StructureDefinition-mii-pr-icu-muv-arterieller-blutdruck.xlsx
+++ b/branches/dependabot/github_actions/dev/actions-3dcd9e0407/StructureDefinition-mii-pr-icu-muv-arterieller-blutdruck.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T22:31:10+00:00</t>
+    <t>2026-10-30T09:20:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
